--- a/データ集約.xlsx
+++ b/データ集約.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a2b93d672871eb8/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a2b93d672871eb8/ドキュメント/Aggregated_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{E2FC29AC-A27B-44BC-B763-C1D62FD82D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10AC6A96-00A1-401D-820B-5A2B298F0167}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{E2FC29AC-A27B-44BC-B763-C1D62FD82D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62EEECF4-BFED-49BF-AED5-85E73905ADDD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5ED11807-3118-49F3-B3F1-0D39459498C3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="マイジャグ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">マイジャグ!$A$2:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">マイジャグ!$A$2:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -97,6 +97,56 @@
       <t>ガッサン</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アナスロ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライゲキ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>曜日</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木</t>
+  </si>
+  <si>
+    <t>木</t>
+    <rPh sb="0" eb="1">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>金</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>月</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>水</t>
   </si>
 </sst>
 </file>
@@ -171,47 +221,44 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -229,6 +276,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,481 +599,534 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9328EFC9-035D-49FE-A259-50354A690619}">
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.25" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="7" customWidth="1"/>
-    <col min="4" max="9" width="9" style="7"/>
-    <col min="10" max="16" width="9" style="11"/>
-    <col min="17" max="23" width="9" style="7"/>
-    <col min="24" max="30" width="9" style="11"/>
-    <col min="31" max="37" width="9" style="7"/>
-    <col min="38" max="44" width="9" style="11"/>
-    <col min="45" max="51" width="9" style="7"/>
-    <col min="52" max="16384" width="9" style="12"/>
+    <col min="1" max="1" width="10.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="5" customWidth="1"/>
+    <col min="5" max="10" width="9" style="5"/>
+    <col min="11" max="17" width="9" style="9"/>
+    <col min="18" max="24" width="9" style="5"/>
+    <col min="25" max="31" width="9" style="9"/>
+    <col min="32" max="38" width="9" style="5"/>
+    <col min="39" max="45" width="9" style="9"/>
+    <col min="46" max="52" width="9" style="5"/>
+    <col min="53" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:52" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="D1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="2" t="s">
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="3" t="s">
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="2" t="s">
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="3" t="s">
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
-      <c r="AR1" s="3"/>
-      <c r="AS1" s="2" t="s">
+      <c r="AN1" s="11"/>
+      <c r="AO1" s="11"/>
+      <c r="AP1" s="11"/>
+      <c r="AQ1" s="11"/>
+      <c r="AR1" s="11"/>
+      <c r="AS1" s="11"/>
+      <c r="AT1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2"/>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-    </row>
-    <row r="2" spans="1:51" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
+      <c r="AU1" s="12"/>
+      <c r="AV1" s="12"/>
+      <c r="AW1" s="12"/>
+      <c r="AX1" s="12"/>
+      <c r="AY1" s="12"/>
+      <c r="AZ1" s="12"/>
+    </row>
+    <row r="2" spans="1:52" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
+      <c r="D2" s="2">
         <v>730</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="2">
         <v>731</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="2">
         <v>732</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="2">
         <v>733</v>
       </c>
-      <c r="G2" s="4">
+      <c r="H2" s="2">
         <v>735</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="2">
         <v>736</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="2">
         <v>737</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>730</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>731</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>732</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>733</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>735</v>
       </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
         <v>736</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>737</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="R2" s="2">
         <v>730</v>
       </c>
-      <c r="R2" s="4">
+      <c r="S2" s="2">
         <v>731</v>
       </c>
-      <c r="S2" s="4">
+      <c r="T2" s="2">
         <v>732</v>
       </c>
-      <c r="T2" s="4">
+      <c r="U2" s="2">
         <v>733</v>
       </c>
-      <c r="U2" s="4">
+      <c r="V2" s="2">
         <v>735</v>
       </c>
-      <c r="V2" s="4">
+      <c r="W2" s="2">
         <v>736</v>
       </c>
-      <c r="W2" s="4">
+      <c r="X2" s="2">
         <v>737</v>
       </c>
-      <c r="X2" s="1">
+      <c r="Y2" s="1">
         <v>730</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="Z2" s="1">
         <v>731</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AA2" s="1">
         <v>732</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AB2" s="1">
         <v>733</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AC2" s="1">
         <v>735</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AD2" s="1">
         <v>736</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AE2" s="1">
         <v>737</v>
       </c>
-      <c r="AE2" s="4">
+      <c r="AF2" s="2">
         <v>730</v>
       </c>
-      <c r="AF2" s="4">
+      <c r="AG2" s="2">
         <v>731</v>
       </c>
-      <c r="AG2" s="4">
+      <c r="AH2" s="2">
         <v>732</v>
       </c>
-      <c r="AH2" s="4">
+      <c r="AI2" s="2">
         <v>733</v>
       </c>
-      <c r="AI2" s="4">
+      <c r="AJ2" s="2">
         <v>735</v>
       </c>
-      <c r="AJ2" s="4">
+      <c r="AK2" s="2">
         <v>736</v>
       </c>
-      <c r="AK2" s="4">
+      <c r="AL2" s="2">
         <v>737</v>
       </c>
-      <c r="AL2" s="1">
+      <c r="AM2" s="1">
         <v>730</v>
       </c>
-      <c r="AM2" s="1">
+      <c r="AN2" s="1">
         <v>731</v>
       </c>
-      <c r="AN2" s="1">
+      <c r="AO2" s="1">
         <v>732</v>
       </c>
-      <c r="AO2" s="1">
+      <c r="AP2" s="1">
         <v>733</v>
       </c>
-      <c r="AP2" s="1">
+      <c r="AQ2" s="1">
         <v>735</v>
       </c>
-      <c r="AQ2" s="1">
+      <c r="AR2" s="1">
         <v>736</v>
       </c>
-      <c r="AR2" s="1">
+      <c r="AS2" s="1">
         <v>737</v>
       </c>
-      <c r="AS2" s="4">
+      <c r="AT2" s="2">
         <v>730</v>
       </c>
-      <c r="AT2" s="4">
+      <c r="AU2" s="2">
         <v>731</v>
       </c>
-      <c r="AU2" s="4">
+      <c r="AV2" s="2">
         <v>732</v>
       </c>
-      <c r="AV2" s="4">
+      <c r="AW2" s="2">
         <v>733</v>
       </c>
-      <c r="AW2" s="4">
+      <c r="AX2" s="2">
         <v>735</v>
       </c>
-      <c r="AX2" s="4">
+      <c r="AY2" s="2">
         <v>736</v>
       </c>
-      <c r="AY2" s="4">
+      <c r="AZ2" s="2">
         <v>737</v>
       </c>
     </row>
-    <row r="3" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="5">
+    <row r="3" spans="1:52" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
         <v>46163</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7">
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5">
         <v>4568</v>
       </c>
-      <c r="D3" s="7">
+      <c r="E3" s="5">
         <v>8585</v>
       </c>
-      <c r="E3" s="7">
+      <c r="F3" s="5">
         <v>5654</v>
       </c>
-      <c r="F3" s="7">
+      <c r="G3" s="5">
         <v>4564</v>
       </c>
-      <c r="G3" s="7">
+      <c r="H3" s="5">
         <v>6456</v>
       </c>
-      <c r="H3" s="7">
+      <c r="I3" s="5">
         <v>447</v>
       </c>
-      <c r="I3" s="7">
+      <c r="J3" s="5">
         <v>470</v>
       </c>
-      <c r="J3" s="8">
+      <c r="K3" s="6">
         <v>3</v>
       </c>
-      <c r="K3" s="8">
+      <c r="L3" s="6">
         <v>7</v>
       </c>
-      <c r="L3" s="8">
+      <c r="M3" s="6">
         <v>21</v>
       </c>
-      <c r="M3" s="8">
+      <c r="N3" s="6">
         <v>15</v>
       </c>
-      <c r="N3" s="8">
+      <c r="O3" s="6">
         <v>4</v>
       </c>
-      <c r="O3" s="8">
+      <c r="P3" s="6">
         <v>15</v>
       </c>
-      <c r="P3" s="8">
+      <c r="Q3" s="6">
         <v>16</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="R3" s="7">
         <v>12</v>
       </c>
-      <c r="R3" s="9">
+      <c r="S3" s="7">
         <v>1</v>
       </c>
-      <c r="S3" s="9">
+      <c r="T3" s="7">
         <v>1</v>
       </c>
-      <c r="T3" s="9">
+      <c r="U3" s="7">
         <v>12</v>
       </c>
-      <c r="U3" s="9">
+      <c r="V3" s="7">
         <v>7</v>
       </c>
-      <c r="V3" s="9">
+      <c r="W3" s="7">
         <v>6</v>
       </c>
-      <c r="W3" s="9">
+      <c r="X3" s="7">
         <v>20</v>
       </c>
-      <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
-      <c r="AG3" s="4"/>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="4"/>
-      <c r="AK3" s="4"/>
-      <c r="AL3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
+      <c r="AL3" s="2"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
       <c r="AP3" s="1"/>
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
-      <c r="AS3" s="4"/>
-      <c r="AT3" s="4"/>
-      <c r="AU3" s="4"/>
-      <c r="AV3" s="4"/>
-      <c r="AW3" s="4"/>
-      <c r="AX3" s="4"/>
-      <c r="AY3" s="4"/>
-    </row>
-    <row r="4" spans="1:51" s="10" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="2"/>
+      <c r="AU3" s="2"/>
+      <c r="AV3" s="2"/>
+      <c r="AW3" s="2"/>
+      <c r="AX3" s="2"/>
+      <c r="AY3" s="2"/>
+      <c r="AZ3" s="2"/>
+    </row>
+    <row r="4" spans="1:52" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
         <v>46164</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="1"/>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="4"/>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="4"/>
-      <c r="AL4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
-      <c r="AS4" s="4"/>
-      <c r="AT4" s="4"/>
-      <c r="AU4" s="4"/>
-      <c r="AV4" s="4"/>
-      <c r="AW4" s="4"/>
-      <c r="AX4" s="4"/>
-      <c r="AY4" s="4"/>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A5" s="5">
+      <c r="AS4" s="1"/>
+      <c r="AT4" s="2"/>
+      <c r="AU4" s="2"/>
+      <c r="AV4" s="2"/>
+      <c r="AW4" s="2"/>
+      <c r="AX4" s="2"/>
+      <c r="AY4" s="2"/>
+      <c r="AZ4" s="2"/>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
         <v>46165</v>
       </c>
-      <c r="B5" s="6"/>
-    </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A6" s="5">
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
         <v>46166</v>
       </c>
-      <c r="B6" s="6"/>
-    </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A7" s="5">
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
         <v>46167</v>
       </c>
-      <c r="B7" s="6"/>
-    </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A8" s="5">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
         <v>46168</v>
       </c>
-      <c r="B8" s="6"/>
-    </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
         <v>46169</v>
       </c>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
         <v>46170</v>
       </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
         <v>46171</v>
       </c>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
         <v>46172</v>
       </c>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A13" s="5">
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
         <v>46173</v>
       </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A14" s="5">
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
         <v>46174</v>
       </c>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A15" s="5">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
         <v>46175</v>
       </c>
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.4">
-      <c r="A16" s="5">
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:52" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
         <v>46176</v>
       </c>
-      <c r="B16" s="6"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="5">
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
         <v>46177</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AL1:AR1"/>
-    <mergeCell ref="AS1:AY1"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="X1:AD1"/>
-    <mergeCell ref="AE1:AK1"/>
+    <mergeCell ref="AM1:AS1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AE1"/>
+    <mergeCell ref="AF1:AL1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
